--- a/public/templates/forms/A-041-DefaultCredentialRemediationLog-FORM.xlsx
+++ b/public/templates/forms/A-041-DefaultCredentialRemediationLog-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="23380" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Log!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -187,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -242,6 +247,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -921,7 +929,7 @@
       <c r="E46" s="11" t="n"/>
       <c r="F46" s="11" t="n"/>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="34.7" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter’s note (internal, delete before publishing): list any [BRACKETED] field that could not be resolved from project context, and any decision needing confirmation.</t>
@@ -968,7 +976,7 @@
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1001,7 +1009,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, findings, sign-off, retention and revision history live on the Log tab.</t>
@@ -1054,10 +1062,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
+      <c r="D7" s="22">
+        <v>46086</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -1082,7 +1088,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Default Account Remediated</t>
@@ -1257,6 +1263,6 @@
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>